--- a/光伏配储项目/电价数据/2026/鳌峰站.xlsx
+++ b/光伏配储项目/电价数据/2026/鳌峰站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5099</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38053</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.53387</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5439400000000001</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.30722</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.31671</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.30757</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43867</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45549</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44022</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.4237</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42004</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40931</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39942</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40135</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38617</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40258</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41376</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.3927</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38555</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41815</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39205</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42107</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41512</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.4251</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41355</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44518</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.2998</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.25248</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29467</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.28277</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>-0.01151</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.11529</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>-0.03051</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.02255</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03604</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08211</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.005019999999999999</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14415</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.2114</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23879</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.15086</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.01415</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.11847</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.01172</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.09415000000000001</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.25355</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.08134999999999999</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.18604</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.42767</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.18044</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.44319</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.07446999999999999</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.2398</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.5588500000000001</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6006900000000001</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.22564</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.28546</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.29488</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.38164</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.41723</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47872</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40031</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41171</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.4208</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.44075</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.15487</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.69274</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.7942</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53662</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5230199999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5063799999999999</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.46517</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.50019</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.37398</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47389</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.35553</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39217</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37174</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35735</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37668</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37664</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38155</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42264</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.51388</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.62391</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7252000000000001</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43614</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.32366</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34621</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.13137</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.29111</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.30165</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.16633</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.12423</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.25731</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.19465</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.14837</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.30857</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.12718</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.29875</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.1636</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.00067</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.06045</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.11487</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.2753</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.14429</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.25539</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.30346</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.21062</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.27571</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.29533</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>-0.00122</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>-0.04162</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.03257</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>-0.01191</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.22395</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.24528</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.35442</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.35205</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.27473</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.25287</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.67647</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.77895</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.7645299999999999</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.78553</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.30114</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.47463</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.13464</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.43933</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.5995</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44024</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43433</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40352</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37658</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35349</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33311</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51646</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.37148</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48525</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37913</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38116</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40248</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.39348</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39111</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38251</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36184</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.4343</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45076</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37181</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39325</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36471</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37065</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35757</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37852</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.4743</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45009</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44456</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39712</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36887</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34681</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.28854</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.29368</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.26187</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.24834</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30534</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.2963</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.27958</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.27464</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.25824</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.13876</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.09254999999999999</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.23107</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.27348</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.01579</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.16928</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29101</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29798</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27767</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.20217</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.15703</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.00564</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.08611000000000001</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.05695</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.1922</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.26657</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.3066</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.18441</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.26728</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.28085</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>-0.00337</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.07894</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.20702</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.22786</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.21394</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.05681</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.14249</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.09223999999999999</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.10219</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.24176</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.2246</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.27688</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34321</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.09814000000000001</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.24976</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.28856</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.24951</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.32827</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.30396</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.30451</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46919</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.3045</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.2973</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.29989</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.29636</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.29416</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.29683</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.34374</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39066</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.32155</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31154</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.29941</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.24824</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.28182</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26455</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.05447999999999999</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.00545</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>-0.03444</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>-0.00975</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.26725</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.23356</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.27589</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.28006</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.37452</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>-0.04447</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.06962</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.16687</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.12389</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.0377</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.0216</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.27665</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.02906</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.09065999999999999</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>-0.02172</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.01948</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.15788</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.27438</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.27487</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.2776</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.02915</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.16869</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.30611</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>-0.008960000000000001</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.30318</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.29651</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29583</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.28357</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.36641</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30043</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30651</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30409</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.28699</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30556</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30455</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.28662</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29058</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.28963</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.28955</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.28942</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29771</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29169</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29477</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3124</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30494</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32447</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33283</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27817</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.25882</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.02443</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.0361</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.03984</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.04393</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.03911</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.03902000000000001</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>-0.01973</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.04489</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.04882</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.14795</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>-0.00134</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.28712</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.05031</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.14647</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.18545</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.27189</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.17605</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.20976</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.11503</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.27637</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.2173</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.28299</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.37937</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.30205</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.30506</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.30372</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39949</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39849</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40979</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.4675299999999999</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35379</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40001</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41332</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34467</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34886</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.24688</v>
+      </c>
+      <c r="D122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E122" t="n">
+        <v>-0.01493</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.28556</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.30768</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.30952</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.28168</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.31066</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.33229</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31459</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33659</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29948</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>-0.04793</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.0466</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04572</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04577000000000001</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04572</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04505</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04321</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04217</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.0447</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10092</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.00273</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04364</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04595</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04297</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04882</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04872</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04488</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04349</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04233</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.0485</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04897</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04243</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.0484</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04478</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04935</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04348</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.07031</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.17669</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.23606</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.25396</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.25451</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.24676</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.28737</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.14359</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.21586</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.19226</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.21128</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.22156</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.19525</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.21653</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.19596</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.24267</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.23587</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.2582</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.29518</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.28146</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.31011</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36746</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36595</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.3305</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31861</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.30568</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40549</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30188</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.2784700000000001</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.25834</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.10166</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29154</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.24663</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.25961</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.24557</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27141</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28149</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.08036</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.05876</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17177</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14839</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16012</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15935</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23739</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21477</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.17518</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.11914</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.2864</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.27621</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29138</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.25823</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.25546</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.25484</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>-0.04022999999999999</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28113</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.29722</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.28058</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.25605</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>-0.0156</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.11788</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.07135</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>-0.00483</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.30558</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.14887</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.10697</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>-0.0036</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.05194</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.10709</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29619</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.17701</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.27438</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>-0.04331</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.16578</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.07659000000000001</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.20409</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47797</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7395</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.48924</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.23445</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.29652</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.57469</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.5189</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.20648</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.48729</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>0.9332</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>-0.0143</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.48786</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>0.68768</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.47294</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>0.97977</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>0.6987000000000001</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.33748</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.78999</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5303300000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7873300000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77674</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87854</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8733300000000001</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.4922</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41177</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39907</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44907</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.2062</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87936</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5513400000000001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6389600000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5382899999999999</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49863</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45904</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42751</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44135</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45127</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39353</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45406</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42119</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40087</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36627</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37626</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41493</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43394</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39189</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.33228</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.35466</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.39594</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45187</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40089</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58704</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42764</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59622</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.45494</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.65489</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>-0.04787</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8204600000000001</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.00296</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>-0.0386</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>-0.04441</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.82911</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>-0.04488</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>-0.04411</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>-0.04433</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>-0.04727000000000001</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>-0.04824000000000001</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>-0.04408</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.09848</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.30968</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.07417</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.10004</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.07108</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.09242</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.06345000000000001</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.08159000000000001</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.0432</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.06279999999999999</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.13888</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.07141</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.04978</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.06441</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>-0.02629</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.06691</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.07643000000000001</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.12773</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.12172</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.13375</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.11728</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.22353</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.28829</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.34395</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41392</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45351</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41627</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39288</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37639</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35437</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.95496</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46758</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40786</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.4197</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.47717</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.3836</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41099</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36608</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34839</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.29143</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40094</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50005</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38767</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37062</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30094</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.0613</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.22781</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>-0.04547</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.25973</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.29331</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>-0.04720000000000001</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.09617000000000001</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.27028</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.25125</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.10086</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.30753</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25415</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.27187</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.29602</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.19303</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.29783</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30946</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31785</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38916</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.38136</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.28255</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42042</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.4017</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5967</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88506</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.33275</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13524</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70345</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7951699999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6496799999999999</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58348</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43745</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41503</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42351</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50052</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41291</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42801</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45039</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.3963</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42349</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.4341</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41291</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39661</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40248</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.37432</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.30878</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.01003</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.22962</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.17072</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.21872</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.22798</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.18875</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.03545</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>-0.00795</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>-0.00925</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>-0.03117</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.12807</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.05438</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.28162</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.03041</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.19535</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38573</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32475</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42458</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32517</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31129</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32054</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39243</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39994</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37494</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35562</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33215</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.27284</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33422</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.30106</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.02105</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.25073</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14877</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14719</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31561</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15174</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.57174</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.60517</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14419</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14383</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14146</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14849</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.27134</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14932</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.27771</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.2803</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14661</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.13148</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11751</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11803</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.17481</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14524</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.15346</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.30581</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33453</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.35202</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31735</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.36947</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36202</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.40641</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40029</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36069</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38488</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45047</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40073</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39357</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40185</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39768</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44077</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43987</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43924</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44416</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44425</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40358</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.3915</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39158</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34931</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5424500000000001</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38957</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46864</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42382</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.4159</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37012</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38105</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38017</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.3937</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38155</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37124</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38156</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36143</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39243</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37127</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38141</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35658</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37154</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38133</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36101</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37505</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.2885</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31244</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30616</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28522</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>-0.04167</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>-0.0348</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.23651</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30251</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24393</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.23526</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26262</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.2974</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28116</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31255</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.28489</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.2543</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30225</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.27197</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.22783</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.28761</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.28846</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.29476</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.27321</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.30825</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.28494</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.2458</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.26194</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.29723</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.3438</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35615</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.29278</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.17992</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41958</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.38987</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36478</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36829</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38028</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38035</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36024</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36616</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41898</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37072</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.38971</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38061</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35282</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34205</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34343</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33859</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34407</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36083</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.31165</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.27323</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.39235</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.28787</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.37579</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.25803</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.25087</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.3178</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.23452</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24903</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.17807</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.06720999999999999</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.16385</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.2403</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.27772</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.30628</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.25084</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.23365</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.26801</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.28146</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.27637</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.25281</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.27741</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.3097200000000001</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.30107</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.39286</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.31237</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.30813</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.28552</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.29829</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.30125</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.30202</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.30404</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.46944</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.3843</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.70497</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.33435</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.33426</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.34195</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.41084</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.26121</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34195</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31433</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30964</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.31449</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.29752</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30491</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.34696</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32554</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32766</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32097</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32393</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.31404</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31413</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32155</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31388</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.27928</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29065</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.2807</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33326</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.30363</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31277</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.29762</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.27281</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.30596</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.33681</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.31785</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37536</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36796</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36836</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36293</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37364</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36223</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39373</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38558</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37164</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40326</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34922</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35147</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35599</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35591</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34632</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36945</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34958</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34863</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.28256</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32607</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32688</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31741</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31905</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31413</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.30946</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32874</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32983</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33598</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35779</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.57686</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.39131</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36235</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37608</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37956</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38069</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.3835</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42967</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40895</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38605</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38557</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6513099999999999</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83368</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47297</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.4079700000000001</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45936</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39337</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35966</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34484</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31402</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.4116</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37668</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37179</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36408</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.3629</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36085</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35686</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.3709</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37956</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35823</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.25957</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.13059</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.28753</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28358</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28218</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19398</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.24204</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27822</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>-0.04862</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27926</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.12727</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28312</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.22545</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28652</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.23655</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30262</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14186</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29531</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.19313</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.20396</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.27549</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.27878</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.29014</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.27942</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.2955</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.27648</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.30515</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.30683</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.28893</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.39974</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.3889</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.63466</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.60172</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.5904700000000001</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.45354</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.61911</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.45171</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.42749</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.44845</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.39586</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37177</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35147</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.47696</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43071</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41973</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37917</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.3751</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36732</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36017</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.48973</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.38852</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.41661</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.42108</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41956</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39937</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40588</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41291</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41053</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41862</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40094</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39726</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41302</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41073</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39452</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38851</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41924</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41723</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39058</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40036</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41311</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45075</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44951</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56088</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50078</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45092</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.40978</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.18209</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.29303</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.37723</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.34674</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.43731</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.19276</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.02214</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.0226</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29911</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.2953</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.30499</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.33722</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.25058</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.20083</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.27476</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.08615</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>-0.04283</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.24569</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.25938</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.70928</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.38413</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.22817</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.08656999999999999</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.03498</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.20296</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.31636</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.2988</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.30665</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.30671</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.29852</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.28803</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.29538</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.30113</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.47944</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.42192</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50463</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.50592</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.35922</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.51455</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.59937</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.37161</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.51509</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.70668</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.45276</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.5319299999999999</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.8048999999999999</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.74041</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.59157</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.64009</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.38112</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.47964</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47951</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47286</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41945</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.49635</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44529</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45842</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43694</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42655</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.4484</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41788</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40086</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45771</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39938</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40711</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39876</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38865</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37694</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37129</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38666</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36654</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36141</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35515</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37968</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39926</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38764</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.38147</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39365</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38664</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36828</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34235</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32383</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.22006</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.23616</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.15041</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.28804</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.18703</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.41626</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.06689000000000001</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.23089</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.40016</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.41956</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.47827</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.46603</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.50402</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.47674</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30948</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.01642</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.19026</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30257</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29277</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35267</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34828</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34818</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.35454</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.35646</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.40824</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.40872</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36324</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41168</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39634</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.37838</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.35464</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.32784</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37796</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38543</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40582</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40104</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34398</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36507</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37808</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39948</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37953</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35509</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39378</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37898</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36407</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44208</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.35309</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.33395</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37675</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.36496</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35577</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35149</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35712</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34845</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33916</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33814</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.32576</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31667</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32458</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.1338</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32677</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.31574</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.23136</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29334</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23283</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.22694</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24601</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>-0.02432</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.12918</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.22429</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.28508</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>-0.02368</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.14898</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04338</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>-0.03631</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.14212</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.1511</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.00496</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30311</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.21544</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.22615</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.13866</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.21022</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.26472</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28277</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.25767</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.29595</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.28482</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.3429700000000001</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30587</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.33486</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.34559</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.3430299999999999</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.32551</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34321</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.3661</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35196</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33884</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31075</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31129</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.3112200000000001</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31103</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31722</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30706</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30706</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30955</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30641</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30706</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30767</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29105</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.2275</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.21697</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.15115</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.18053</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01429</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.00344</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>-0.03908</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.03429</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.16998</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.21487</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.26771</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.24225</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.24478</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.24455</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.25023</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.26378</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.28696</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.27246</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.26892</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.25803</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30354</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.27733</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.28178</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.26583</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.26804</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.28413</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.27408</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.29466</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.36296</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.30154</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.30566</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.28576</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.25667</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.26698</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.25229</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.23673</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.19064</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.05696</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29788</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.41496</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.03295</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.06623999999999999</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.25012</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.22709</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.22433</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.1481</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.26952</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.26334</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.24583</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.22303</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.20664</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.19003</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.21488</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.22574</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.17017</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.2227</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.22235</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.24388</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.23206</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.2153</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.26368</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.22685</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.26985</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.32559</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.2712</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.24692</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.24754</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.18418</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.06597</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.49679</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.50096</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.02075</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.18002</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.19589</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.09806000000000001</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.04352</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.04785</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.00667</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.20736</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.03113</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.29116</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.04789</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.02658</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.13132</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.03985</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.04236</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>-0.004929999999999999</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.0736</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.02598</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>-0.02513</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.02086</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.05194</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.18879</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.25227</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.20343</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.22599</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.25419</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.25913</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.25619</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.28561</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.25995</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.28757</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.27613</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.25206</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.28444</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.2609</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.29284</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.29618</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.28497</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.2886</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.28981</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.33909</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.27647</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.29667</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.3027</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.29237</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32495</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35413</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36535</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33508</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.08738</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32746</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33383</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.3415899999999999</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.00199</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>-0.009560000000000001</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>-0.00294</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>-0.01772</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.30479</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>-0.04309</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.23025</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.26002</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.28221</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.2774</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.27022</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.28969</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.25461</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30787</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.30504</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.27808</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.09926</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.21138</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26937</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30287</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.30944</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.14947</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.3173</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31174</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.13726</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.04774</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30804</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.28925</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33559</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34621</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.32797</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.31572</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31767</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.31744</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.31282</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.31593</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.30643</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.30814</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37065</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31316</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>-0.009380000000000001</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.31258</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.30121</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.29697</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.31722</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36785</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31374</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33078</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.3703</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.26321</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34508</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.28844</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32048</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36924</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35528</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>-0.00114</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.29264</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.42311</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.29421</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.52103</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.02103</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.26011</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.26206</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.30541</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.2389</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.20719</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.23336</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.22123</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.20163</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.20309</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30422</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.35891</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.26957</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.20283</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.23712</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.23987</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34207</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36328</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32398</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.16956</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.22588</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.26936</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.25358</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.25377</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.22088</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.29511</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.36403</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.41368</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.4056</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.42664</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.36141</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.27123</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.29932</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.42236</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.38775</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.33834</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.37071</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42479</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.70589</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.41769</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40276</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45864</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38006</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3727200000000001</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36434</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36876</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.44142</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40097</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40102</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39159</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38077</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37561</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37448</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37867</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37738</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36921</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.3711</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39972</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36959</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.28433</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.09612999999999999</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.27995</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.0319</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.02642</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.04572</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>-0.04416</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>-0.0105</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.31266</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.27649</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.0876</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.2973</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.16351</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.30424</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.28734</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.2877</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.2567</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.27458</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.26607</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.14093</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.30571</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.15153</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.18217</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.02288</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.07271999999999999</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.29661</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.25766</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.26105</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.2811</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.29033</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.32272</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.38657</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.36337</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.42458</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.52562</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.52059</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.45618</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.54641</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.42271</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.30271</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.43986</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.34735</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.49422</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.47567</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.70699</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.74509</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.5139900000000001</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.51588</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39839</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44087</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.36683</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37935</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37525</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.2714</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37071</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32104</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33459</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33559</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.3135</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32685</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.30991</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.30532</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.30933</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.30971</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.29301</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.29248</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36311</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.30499</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.29142</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.2867</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.28111</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.27478</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.25785</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.25599</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.27301</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.20393</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.22973</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.13296</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>-0.01698</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.02657</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.2393</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.01643</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.03353</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.02166</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.00618</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>-0.00148</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.11755</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.10923</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.20204</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.18201</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.10372</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.22983</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.22154</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.29516</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33911</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.21795</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.29035</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.37211</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.39151</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.29058</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.37257</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.28492</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.39018</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.37148</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.37193</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.39725</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.37627</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.25877</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.38208</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.35203</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.35311</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.3731</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.38121</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37619</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.75846</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.33644</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.40008</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.37344</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.33645</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33738</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.35539</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38219</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.34773</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34213</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37984</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.3794</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.34872</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36328</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36426</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35591</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36594</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35216</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.30258</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.30434</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.29661</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.26412</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.23314</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.21121</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.20247</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.16982</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.17022</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.17489</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.22961</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.05978</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>-0.02319</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>-0.03545</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>-0.03403</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.01255</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.0762</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.00809</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.02722</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01017</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>-0.0317</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>-0.03868</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.02083</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.04218</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>-0.03755</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>-0.0304</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.13414</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>-0.01337</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.13813</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.15843</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.2027</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.36631</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>-0.00408</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.02177</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.02907</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.34341</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.46785</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.48448</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.4431</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.35149</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.53604</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.38089</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.47457</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39878</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.39856</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.41596</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.32093</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.44455</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.34511</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39765</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.40218</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.38798</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.37733</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.37235</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.39092</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.49689</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.40267</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.40583</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37399</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36957</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35077</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41956</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.3792</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34351</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33333</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.31714</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32047</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35577</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.3423</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.29512</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.25899</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.22347</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.20376</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.13603</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.18239</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.22382</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.21053</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.13348</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.1412</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.01407</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.11582</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.03019</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.03163</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.03306</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.03698</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.03071</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.01586</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>-0.04701</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03875</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>-0.02435</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>-0.03273</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>-0.04354</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.09265999999999999</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>-0.04181</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>-0.04778</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>-0.04177</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.03207</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>-0.04125</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>-0.04774</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>-0.03191</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>-0.02249</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>-0.03698</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>-0.03633</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>-0.0256</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.18317</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.21587</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.23524</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.23813</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.24391</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.25904</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.26551</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.26721</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.29975</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.39583</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.31474</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.28643</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.3781600000000001</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38312</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40907</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.38219</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.47731</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.38498</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41988</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.43508</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41386</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39528</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40874</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40985</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.384</v>
       </c>
     </row>
   </sheetData>
